--- a/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala)</t>
+          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,21; 70,13</t>
+          <t>64,39; 70,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54,99; 65,86</t>
+          <t>55,5; 65,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,27; 66,58</t>
+          <t>59,63; 66,59</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,59; 69,17</t>
+          <t>64,32; 68,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,92; 66,28</t>
+          <t>61,88; 66,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,58; 66,77</t>
+          <t>63,54; 66,77</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,88; 68,01</t>
+          <t>57,79; 68,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,84; 71,45</t>
+          <t>65,21; 71,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,73; 68,74</t>
+          <t>61,27; 68,65</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,24; 66,93</t>
+          <t>62,38; 67,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,1; 65,8</t>
+          <t>61,02; 65,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,25; 65,54</t>
+          <t>62,28; 65,72</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>62,53; 66,91</t>
+          <t>62,67; 66,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,82; 66,11</t>
+          <t>62,74; 66,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,48; 66,02</t>
+          <t>63,26; 66,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por tutor (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,39; 70,41</t>
+          <t>64,35; 70,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,5; 65,3</t>
+          <t>55,0; 65,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,63; 66,59</t>
+          <t>59,54; 66,66</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,32; 68,82</t>
+          <t>64,51; 68,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,88; 66,21</t>
+          <t>61,93; 66,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,54; 66,77</t>
+          <t>63,51; 66,7</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,79; 68,18</t>
+          <t>57,96; 68,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,21; 71,6</t>
+          <t>64,94; 72,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,27; 68,65</t>
+          <t>60,88; 68,45</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,38; 67,08</t>
+          <t>62,56; 67,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,02; 65,43</t>
+          <t>61,08; 65,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,28; 65,72</t>
+          <t>62,52; 65,73</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>62,67; 66,91</t>
+          <t>62,34; 66,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,74; 66,11</t>
+          <t>62,85; 66,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,26; 66,08</t>
+          <t>63,3; 66,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
@@ -489,18 +489,18 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>67,3</t>
+          <t>63,74</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62,05</t>
+          <t>67,32</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64,18</t>
+          <t>65,32</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>64,35; 70,66</t>
+          <t>60,69; 66,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,0; 65,84</t>
+          <t>64,13; 70,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59,54; 66,66</t>
+          <t>63,15; 67,73</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66,69</t>
+          <t>64,17</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>64,1</t>
+          <t>66,71</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65,14</t>
+          <t>65,24</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,51; 68,96</t>
+          <t>62,03; 66,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,93; 66,2</t>
+          <t>64,58; 69,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,51; 66,7</t>
+          <t>63,68; 66,81</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63,82</t>
+          <t>68,59</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>68,23</t>
+          <t>66,92</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65,95</t>
+          <t>67,82</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,96; 68,24</t>
+          <t>65,34; 71,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,94; 72,1</t>
+          <t>64,26; 69,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,88; 68,45</t>
+          <t>65,61; 69,92</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>64,67</t>
+          <t>62,99</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63,35</t>
+          <t>64,61</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>64,01</t>
+          <t>63,84</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>62,56; 67,1</t>
+          <t>60,81; 65,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>61,08; 65,56</t>
+          <t>62,18; 66,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62,52; 65,73</t>
+          <t>62,09; 65,36</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>65,35</t>
+          <t>64,93</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64,57</t>
+          <t>66,28</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,93</t>
+          <t>65,55</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>62,34; 66,79</t>
+          <t>63,64; 66,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,85; 66,07</t>
+          <t>65,07; 67,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63,3; 66,01</t>
+          <t>64,65; 66,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/KP10in_T-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -97,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -110,6 +112,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -489,7 +494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 100,0%)</t>
+          <t>KIDSCREEN percibido por adulto/a (escala) (tasa de respuesta: 49,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -546,149 +551,109 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>63,74</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>67,32</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>65,32</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>63.7350042401149</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>67.31572066855048</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>65.31743088539464</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>60,69; 66,95</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>64,13; 70,35</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>63,15; 67,73</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>60.68814769922665</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>64.13217689651486</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>63.15461929968885</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>66.9494367318394</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>70.35469027994272</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>67.72862845418965</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>64,17</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>66,71</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>62,03; 66,38</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>64,58; 69,22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>63,68; 66,81</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>64.16815070518155</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>66.70906308788564</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>65.23524166245863</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>68,59</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>66,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>67,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>62.03223368980152</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>64.58101104241295</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>63.67891820279642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>65,34; 71,82</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>64,26; 69,72</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>65,61; 69,92</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>66.37591967397879</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>69.21851544975765</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>66.80993845757051</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -696,97 +661,162 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>62,99</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>64,61</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>63,84</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>68.592716790548</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>66.91901731353614</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>67.82360840276087</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>60,81; 65,27</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>62,18; 66,92</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62,09; 65,36</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>65.34306560447789</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>64.25740303743885</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>65.6064430625009</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>71.82458015849511</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>69.71744667065272</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>69.91787500856086</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>62.99407072363657</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>64.60889573439599</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>63.83749205118404</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>60.81149261863509</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>62.18340177164453</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>62.09081383421274</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>65.27160767292391</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>66.91669726697408</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>65.35572278459895</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>64,93</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>66,28</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>65,55</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>63,64; 66,39</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>65,07; 67,66</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>64,65; 66,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>64.92732094460014</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>66.28067204261059</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>65.54846297643974</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>63.64034898981852</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>65.06789259723863</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>64.65044445765709</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>66.38548833554718</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>67.65564031366436</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>66.48919769510343</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -794,12 +824,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
